--- a/DOM/AFOLU/B1_Model_Structure.xlsx
+++ b/DOM/AFOLU/B1_Model_Structure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{B4B74CD5-98CA-4099-8BEE-8F5FA353F6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DF59ECC-F627-4CFA-9EB3-35829C9B9E5E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1462E6A9-4C07-4006-B90D-2E498328808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sets" sheetId="1" r:id="rId1"/>
@@ -14,8 +14,8 @@
     <sheet name="sector" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">sector!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$3:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">sector!$A$1:$D$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sets!$A$3:$L$295</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -29,9 +29,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -67,7 +68,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A104" authorId="0" shapeId="0" xr:uid="{093965C2-227A-475E-9467-EBCD8D09B795}">
+    <comment ref="A42" authorId="0" shapeId="0" xr:uid="{093965C2-227A-475E-9467-EBCD8D09B795}">
       <text>
         <r>
           <rPr>
@@ -86,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="623">
   <si>
     <t>set</t>
   </si>
@@ -1879,15 +1880,9 @@
     <t>SpecificSector</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>Otro</t>
   </si>
   <si>
-    <t>Energia</t>
-  </si>
-  <si>
     <t>AFOLU</t>
   </si>
   <si>
@@ -1900,22 +1895,67 @@
     <t>Ganaderia</t>
   </si>
   <si>
-    <t>Waste</t>
-  </si>
-  <si>
-    <t>Residuos</t>
-  </si>
-  <si>
-    <t>IPPU</t>
-  </si>
-  <si>
-    <t>PIUP</t>
-  </si>
-  <si>
     <t>Bosques remociones</t>
   </si>
   <si>
-    <t>Transporte</t>
+    <t>PPADSL</t>
+  </si>
+  <si>
+    <t>PPAFOI</t>
+  </si>
+  <si>
+    <t>PPANGS</t>
+  </si>
+  <si>
+    <t>PPDBGS</t>
+  </si>
+  <si>
+    <t>PPDDSL</t>
+  </si>
+  <si>
+    <t>PPDFOI</t>
+  </si>
+  <si>
+    <t>PPDNGS</t>
+  </si>
+  <si>
+    <t>PPDGSL</t>
+  </si>
+  <si>
+    <t>PPDGLP</t>
+  </si>
+  <si>
+    <t>PPDBIM</t>
+  </si>
+  <si>
+    <t>PPDHYD</t>
+  </si>
+  <si>
+    <t>CO2e_AP</t>
+  </si>
+  <si>
+    <t>E5CAMFOR</t>
+  </si>
+  <si>
+    <t>E5CAMCUL</t>
+  </si>
+  <si>
+    <t>E5CAMPAS</t>
+  </si>
+  <si>
+    <t>E5CAMASENTA</t>
+  </si>
+  <si>
+    <t>CAMFOR</t>
+  </si>
+  <si>
+    <t>CAMCUL</t>
+  </si>
+  <si>
+    <t>CAMPAS</t>
+  </si>
+  <si>
+    <t>CAMASENTA</t>
   </si>
 </sst>
 </file>
@@ -1952,24 +1992,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1997,36 +2025,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0E6F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE1BF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCFFFF5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2050,39 +2060,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2090,28 +2093,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2399,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:L299"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2496,47 +2495,47 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <f>+COUNTA(B4:B1048576)</f>
+        <f t="shared" ref="B3:L3" si="0">+COUNTA(B4:B1048576)</f>
         <v>33</v>
       </c>
       <c r="C3">
-        <f>+COUNTA(C4:C1048576)</f>
-        <v>281</v>
+        <f t="shared" si="0"/>
+        <v>296</v>
       </c>
       <c r="D3">
-        <f>+COUNTA(D4:D1048576)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E3">
-        <f>+COUNTA(E4:E1048576)</f>
-        <v>181</v>
+        <f t="shared" si="0"/>
+        <v>185</v>
       </c>
       <c r="F3">
-        <f>+COUNTA(F4:F1048576)</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="G3">
-        <f>+COUNTA(G4:G1048576)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H3">
-        <f>+COUNTA(H4:H1048576)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I3">
-        <f>+COUNTA(I4:I1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J3">
-        <f>+COUNTA(J4:J1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3">
-        <f>+COUNTA(K4:K1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f>+COUNTA(L4:L1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2798,7 +2797,7 @@
         <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>614</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -2812,7 +2811,7 @@
         <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -2826,7 +2825,7 @@
         <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -2839,8 +2838,8 @@
       <c r="E24" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>89</v>
+      <c r="F24" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -2853,6 +2852,9 @@
       <c r="E25" t="s">
         <v>91</v>
       </c>
+      <c r="F25" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26">
@@ -4012,7 +4014,7 @@
       <c r="C166" t="s">
         <v>368</v>
       </c>
-      <c r="E166" s="10" t="s">
+      <c r="E166" s="4" t="s">
         <v>369</v>
       </c>
     </row>
@@ -4020,7 +4022,7 @@
       <c r="C167" t="s">
         <v>370</v>
       </c>
-      <c r="E167" s="10" t="s">
+      <c r="E167" s="4" t="s">
         <v>371</v>
       </c>
     </row>
@@ -4028,7 +4030,7 @@
       <c r="C168" t="s">
         <v>372</v>
       </c>
-      <c r="E168" s="10" t="s">
+      <c r="E168" s="4" t="s">
         <v>373</v>
       </c>
     </row>
@@ -4036,7 +4038,7 @@
       <c r="C169" t="s">
         <v>374</v>
       </c>
-      <c r="E169" s="10" t="s">
+      <c r="E169" s="4" t="s">
         <v>375</v>
       </c>
     </row>
@@ -4044,7 +4046,7 @@
       <c r="C170" t="s">
         <v>376</v>
       </c>
-      <c r="E170" s="10" t="s">
+      <c r="E170" s="4" t="s">
         <v>377</v>
       </c>
     </row>
@@ -4052,7 +4054,7 @@
       <c r="C171" t="s">
         <v>378</v>
       </c>
-      <c r="E171" s="10" t="s">
+      <c r="E171" s="4" t="s">
         <v>379</v>
       </c>
     </row>
@@ -4060,7 +4062,7 @@
       <c r="C172" t="s">
         <v>380</v>
       </c>
-      <c r="E172" s="10" t="s">
+      <c r="E172" s="4" t="s">
         <v>381</v>
       </c>
     </row>
@@ -4068,7 +4070,7 @@
       <c r="C173" t="s">
         <v>382</v>
       </c>
-      <c r="E173" s="10" t="s">
+      <c r="E173" s="4" t="s">
         <v>383</v>
       </c>
     </row>
@@ -4076,7 +4078,7 @@
       <c r="C174" t="s">
         <v>384</v>
       </c>
-      <c r="E174" s="10" t="s">
+      <c r="E174" s="4" t="s">
         <v>385</v>
       </c>
     </row>
@@ -4084,7 +4086,7 @@
       <c r="C175" t="s">
         <v>386</v>
       </c>
-      <c r="E175" s="10" t="s">
+      <c r="E175" s="4" t="s">
         <v>387</v>
       </c>
     </row>
@@ -4092,7 +4094,7 @@
       <c r="C176" t="s">
         <v>388</v>
       </c>
-      <c r="E176" s="10" t="s">
+      <c r="E176" s="4" t="s">
         <v>389</v>
       </c>
     </row>
@@ -4100,7 +4102,7 @@
       <c r="C177" t="s">
         <v>390</v>
       </c>
-      <c r="E177" s="10" t="s">
+      <c r="E177" s="4" t="s">
         <v>391</v>
       </c>
     </row>
@@ -4108,7 +4110,7 @@
       <c r="C178" t="s">
         <v>392</v>
       </c>
-      <c r="E178" s="10" t="s">
+      <c r="E178" s="4" t="s">
         <v>393</v>
       </c>
     </row>
@@ -4116,7 +4118,7 @@
       <c r="C179" t="s">
         <v>394</v>
       </c>
-      <c r="E179" s="10" t="s">
+      <c r="E179" s="4" t="s">
         <v>395</v>
       </c>
     </row>
@@ -4124,7 +4126,7 @@
       <c r="C180" t="s">
         <v>396</v>
       </c>
-      <c r="E180" s="10" t="s">
+      <c r="E180" s="4" t="s">
         <v>397</v>
       </c>
     </row>
@@ -4132,7 +4134,7 @@
       <c r="C181" t="s">
         <v>398</v>
       </c>
-      <c r="E181" s="10" t="s">
+      <c r="E181" s="4" t="s">
         <v>399</v>
       </c>
     </row>
@@ -4140,7 +4142,7 @@
       <c r="C182" t="s">
         <v>400</v>
       </c>
-      <c r="E182" s="10" t="s">
+      <c r="E182" s="4" t="s">
         <v>401</v>
       </c>
     </row>
@@ -4148,15 +4150,15 @@
       <c r="C183" t="s">
         <v>402</v>
       </c>
-      <c r="E183" s="10" t="s">
+      <c r="E183" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="184" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C184" t="s">
         <v>404</v>
       </c>
-      <c r="E184" s="10" t="s">
+      <c r="E184" s="4" t="s">
         <v>405</v>
       </c>
     </row>
@@ -4164,49 +4166,57 @@
       <c r="C185" t="s">
         <v>406</v>
       </c>
-      <c r="E185" s="10"/>
+      <c r="E185" s="11" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C186" t="s">
         <v>407</v>
       </c>
-      <c r="E186" s="10"/>
+      <c r="E186" s="12" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C187" t="s">
         <v>408</v>
       </c>
-      <c r="E187" s="10"/>
+      <c r="E187" s="12" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C188" t="s">
         <v>409</v>
       </c>
-      <c r="E188" s="10"/>
+      <c r="E188" s="12" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="189" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>410</v>
       </c>
-      <c r="E189" s="10"/>
+      <c r="E189" s="4"/>
     </row>
     <row r="190" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
         <v>411</v>
       </c>
-      <c r="E190" s="10"/>
+      <c r="E190" s="4"/>
     </row>
     <row r="191" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
         <v>412</v>
       </c>
-      <c r="E191" s="10"/>
+      <c r="E191" s="4"/>
     </row>
     <row r="192" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
         <v>413</v>
       </c>
-      <c r="E192" s="10"/>
+      <c r="E192" s="4"/>
     </row>
     <row r="193" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
@@ -4294,384 +4304,457 @@
       </c>
     </row>
     <row r="210" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C210" s="10" t="s">
+      <c r="C210" s="4" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="211" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C211" s="10" t="s">
+      <c r="C211" s="4" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="212" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C212" s="10" t="s">
+      <c r="C212" s="4" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="213" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C213" s="10" t="s">
+      <c r="C213" s="4" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="214" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C214" s="10" t="s">
+      <c r="C214" s="4" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="215" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C215" s="10" t="s">
+      <c r="C215" s="4" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="216" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C216" s="10" t="s">
+      <c r="C216" s="4" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="217" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C217" s="10" t="s">
+      <c r="C217" s="4" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="218" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C218" s="10" t="s">
+      <c r="C218" s="4" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="219" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C219" s="10" t="s">
+      <c r="C219" s="4" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="220" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C220" s="10" t="s">
+      <c r="C220" s="4" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="221" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C221" s="10" t="s">
+      <c r="C221" s="4" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="222" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C222" s="10" t="s">
+      <c r="C222" s="4" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="223" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C223" s="10" t="s">
+      <c r="C223" s="4" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="224" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C224" s="10" t="s">
+      <c r="C224" s="4" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C225" s="10" t="s">
+      <c r="C225" s="4" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C226" s="10" t="s">
+      <c r="C226" s="4" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C227" s="10" t="s">
+      <c r="C227" s="4" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C228" s="10" t="s">
+      <c r="C228" s="4" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C229" s="10" t="s">
+      <c r="C229" s="4" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C230" s="10" t="s">
+      <c r="C230" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C231" s="10" t="s">
+      <c r="C231" s="4" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C232" s="10" t="s">
+      <c r="C232" s="4" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C233" s="10" t="s">
+      <c r="C233" s="4" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C234" s="10" t="s">
+      <c r="C234" s="4" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C235" s="10" t="s">
+      <c r="C235" s="4" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C236" s="10" t="s">
+      <c r="C236" s="4" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C237" s="10" t="s">
+      <c r="C237" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C238" s="10" t="s">
+      <c r="C238" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C239" s="10" t="s">
+      <c r="C239" s="4" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C240" s="10" t="s">
+      <c r="C240" s="4" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C241" s="10" t="s">
+      <c r="C241" s="4" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C242" s="10" t="s">
+      <c r="C242" s="4" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C243" s="10" t="s">
+      <c r="C243" s="4" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C244" s="10" t="s">
+      <c r="C244" s="4" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C245" s="10" t="s">
+      <c r="C245" s="4" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C246" s="10" t="s">
+      <c r="C246" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C247" s="10" t="s">
+      <c r="C247" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C248" s="10" t="s">
+      <c r="C248" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C249" s="10" t="s">
+      <c r="C249" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C250" s="10" t="s">
+      <c r="C250" s="4" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C251" s="10" t="s">
+      <c r="C251" s="4" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C252" s="10" t="s">
+      <c r="C252" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C253" s="10" t="s">
+      <c r="C253" s="4" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C254" s="10" t="s">
+      <c r="C254" s="4" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C255" s="10" t="s">
+      <c r="C255" s="4" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C256" s="10" t="s">
+      <c r="C256" s="4" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C257" s="10" t="s">
+      <c r="C257" s="4" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C258" s="10" t="s">
+      <c r="C258" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C259" s="10" t="s">
+      <c r="C259" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C260" s="10" t="s">
+      <c r="C260" s="4" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C261" s="10" t="s">
+      <c r="C261" s="4" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C262" s="10" t="s">
+      <c r="C262" s="4" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C263" s="10" t="s">
+      <c r="C263" s="4" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C264" s="10" t="s">
+      <c r="C264" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C265" s="10" t="s">
+      <c r="C265" s="4" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C266" s="10" t="s">
+      <c r="C266" s="4" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C267" s="10" t="s">
+      <c r="C267" s="4" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C268" s="10" t="s">
+      <c r="C268" s="4" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C269" s="10" t="s">
+      <c r="C269" s="4" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C270" s="10" t="s">
+      <c r="C270" s="4" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C271" s="10" t="s">
+      <c r="C271" s="4" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C272" s="10" t="s">
+      <c r="C272" s="4" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C273" s="10" t="s">
+      <c r="C273" s="4" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C274" s="10" t="s">
+      <c r="C274" s="4" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C275" s="10" t="s">
+      <c r="C275" s="4" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C276" s="10" t="s">
+      <c r="C276" s="4" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C277" s="10" t="s">
+      <c r="C277" s="4" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C278" s="10" t="s">
+      <c r="C278" s="4" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C279" s="11" t="s">
+      <c r="C279" s="5" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C280" s="11" t="s">
+      <c r="C280" s="5" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C281" s="11" t="s">
+      <c r="C281" s="5" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C282" s="11" t="s">
+      <c r="C282" s="5" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C283" s="11" t="s">
+      <c r="C283" s="5" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C284" s="11" t="s">
+      <c r="C284" s="5" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C285" s="10"/>
+      <c r="C285" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C286" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C287" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C288" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C289" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C290" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C291" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C292" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C293" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C294" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="295" spans="3:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C295" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C296" s="11" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C297" s="12" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C298" s="12" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C299" s="12" t="s">
+        <v>622</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:L295" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -6081,14 +6164,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED10C39E-557A-4278-BB05-98C0EDA618C0}">
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -6107,4039 +6190,1080 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D2" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D20" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>84</v>
+      <c r="A21" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D21" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D22" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>90</v>
+      <c r="A23" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D25" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>118</v>
+        <v>240</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>602</v>
+        <v>597</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>603</v>
+        <v>597</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>124</v>
+        <v>246</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>603</v>
+        <v>597</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>603</v>
+        <v>597</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>603</v>
+        <v>597</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>130</v>
+        <v>252</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>603</v>
+        <v>597</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>132</v>
+        <v>358</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>603</v>
-      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>134</v>
+      <c r="A45" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>136</v>
+      <c r="A46" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>138</v>
+      <c r="A47" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>140</v>
+      <c r="A48" s="3" t="s">
+        <v>372</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>142</v>
+      <c r="A49" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>144</v>
+      <c r="A50" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>146</v>
+      <c r="A51" s="3" t="s">
+        <v>364</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>148</v>
+      <c r="A52" s="3" t="s">
+        <v>366</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>150</v>
+      <c r="A53" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>152</v>
+      <c r="A54" s="3" t="s">
+        <v>374</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>154</v>
+      <c r="A55" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>156</v>
+      <c r="A56" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>158</v>
+      <c r="A57" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>160</v>
+      <c r="A58" s="3" t="s">
+        <v>382</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
-        <v>162</v>
+      <c r="A59" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>164</v>
+      <c r="A60" s="3" t="s">
+        <v>386</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
-        <v>166</v>
+      <c r="A61" s="3" t="s">
+        <v>392</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>133</v>
+      <c r="A62" s="3" t="s">
+        <v>396</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>607</v>
+        <v>597</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
-        <v>135</v>
+      <c r="A63" s="3" t="s">
+        <v>388</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>607</v>
+        <v>597</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>170</v>
+      <c r="A64" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>607</v>
+        <v>597</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>172</v>
+        <v>390</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>174</v>
+        <v>406</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>176</v>
+        <v>394</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>178</v>
+        <v>398</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>184</v>
+        <v>407</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>186</v>
+        <v>408</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>188</v>
+        <v>409</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>190</v>
+        <v>410</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>192</v>
+        <v>411</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>194</v>
+        <v>412</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>196</v>
+        <v>413</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D82" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D84" s="19" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>603</v>
-      </c>
-      <c r="G105" s="10"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D106" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D108" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D109" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D110" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D114" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D115" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D116" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D117" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D119" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D120" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D121" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D122" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D125" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D126" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D127" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D128" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D131" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D132" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D134" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D135" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D137" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D138" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D139" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D140" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D141" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D143" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D144" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D145" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D146" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D147" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D148" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D149" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D150" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D151" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D152" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D153" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D154" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D155" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D156" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D157" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D158" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D159" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D160" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D161" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D162" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D163" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D164" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D165" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D166" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D167" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D173" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D174" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D175" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D177" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D178" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D179" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D180" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D182" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D183" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D184" s="14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D185" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D186" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D187" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C188" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D190" s="13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D191" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C192" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D192" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D193" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="D194" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D195" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D196" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D197" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D198" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C199" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D199" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D200" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D201" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A202" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="B202" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D202" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A203" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C203" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D203" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A204" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="B204" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D204" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A205" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C205" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D205" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D206" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D207" s="20" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C208" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D208" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F208" s="10"/>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D209" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F209" s="10"/>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D210" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F210" s="10"/>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A211" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C211" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D211" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F211" s="10"/>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="B212" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C212" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D212" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F212" s="10"/>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A213" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C213" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D213" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F213" s="10"/>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A214" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C214" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D214" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F214" s="10"/>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A215" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C215" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D215" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F215" s="10"/>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D216" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F216" s="10"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A217" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C217" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D217" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F217" s="10"/>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="B218" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C218" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D218" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F218" s="10"/>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D219" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F219" s="10"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A220" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="B220" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C220" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D220" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F220" s="10"/>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A221" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C221" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D221" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F221" s="10"/>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A222" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C222" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D222" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F222" s="10"/>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A223" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C223" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D223" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F223" s="10"/>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A224" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C224" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D224" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F224" s="10"/>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A225" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C225" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D225" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F225" s="10"/>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C226" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D226" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F226" s="10"/>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A227" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C227" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D227" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F227" s="10"/>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A228" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C228" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D228" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F228" s="10"/>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A229" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C229" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D229" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F229" s="10"/>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A230" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B230" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C230" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D230" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F230" s="10"/>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A231" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C231" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D231" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F231" s="10"/>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A232" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C232" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D232" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F232" s="10"/>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A233" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C233" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D233" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F233" s="10"/>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A234" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C234" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D234" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F234" s="10"/>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A235" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="B235" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D235" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F235" s="10"/>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A236" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C236" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D236" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F236" s="10"/>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A237" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C237" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D237" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F237" s="10"/>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A238" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C238" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D238" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F238" s="10"/>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A239" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C239" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D239" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F239" s="10"/>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A240" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D240" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F240" s="10"/>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A241" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C241" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D241" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F241" s="10"/>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A242" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C242" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D242" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F242" s="10"/>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A243" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C243" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D243" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F243" s="10"/>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A244" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C244" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D244" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F244" s="10"/>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A245" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C245" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D245" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F245" s="10"/>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A246" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C246" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D246" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F246" s="10"/>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="B247" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C247" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D247" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F247" s="10"/>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A248" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C248" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D248" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F248" s="10"/>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A249" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C249" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D249" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F249" s="10"/>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A250" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="B250" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C250" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D250" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F250" s="10"/>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A251" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C251" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D251" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F251" s="10"/>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A252" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C252" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D252" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F252" s="10"/>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A253" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C253" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D253" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F253" s="10"/>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A254" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C254" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D254" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F254" s="10"/>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="B255" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C255" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D255" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F255" s="10"/>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C256" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D256" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F256" s="10"/>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A257" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="B257" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C257" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D257" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F257" s="10"/>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C258" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D258" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F258" s="10"/>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A259" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C259" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D259" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F259" s="10"/>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C260" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D260" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F260" s="10"/>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C261" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D261" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F261" s="10"/>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A262" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="B262" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C262" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D262" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F262" s="10"/>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A263" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C263" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D263" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F263" s="10"/>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A264" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C264" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D264" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F264" s="10"/>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A265" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="B265" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C265" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D265" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F265" s="10"/>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A266" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C266" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D266" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F266" s="10"/>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A267" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C267" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D267" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F267" s="10"/>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A268" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C268" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D268" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F268" s="10"/>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A269" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C269" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D269" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F269" s="10"/>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A270" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C270" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D270" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F270" s="10"/>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A271" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C271" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D271" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F271" s="10"/>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A272" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C272" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D272" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F272" s="10"/>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A273" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C273" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D273" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F273" s="10"/>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A274" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C274" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D274" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F274" s="10"/>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A275" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="B275" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C275" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D275" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F275" s="10"/>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A276" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="D276" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="F276" s="10"/>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A277" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D277" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A278" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D278" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A279" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C279" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D279" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A280" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D280" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A281" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D281" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A282" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D282" s="18" t="s">
-        <v>605</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D282" xr:uid="{51B380EC-F6E5-4369-BC41-BC40A47B4895}"/>
+  <autoFilter ref="A1:D77" xr:uid="{51B380EC-F6E5-4369-BC41-BC40A47B4895}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c2c21c4-f980-47d5-be5b-1bb924ee96a2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D404091916B8749A73FDE0336A1D2B1" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97d759966af21adcadc0b99feda85e1a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="160a8fee-1065-46af-a09f-4bc299cd7729" xmlns:ns3="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4a9b885529ac7a0313cb8fba8dc54f0" ns2:_="" ns3:_="">
+    <xsd:import namespace="160a8fee-1065-46af-a09f-4bc299cd7729"/>
+    <xsd:import namespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -10148,18 +7272,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10167,7 +7286,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="160a8fee-1065-46af-a09f-4bc299cd7729" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -10180,91 +7299,52 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:displayName="Etiquetas de imagen_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{358d400d-8031-419e-a2bc-623ab747dbff}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -10276,8 +7356,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -10366,12 +7446,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="160a8fee-1065-46af-a09f-4bc299cd7729" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E67016B-2BB4-478C-AF15-1A9FF8562EBE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F371C454-B910-4AEA-BAC8-D609F5F5142F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10385,5 +7479,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27A6513A-5460-4AA3-B9C8-95B05891DFE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E67016B-2BB4-478C-AF15-1A9FF8562EBE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>